--- a/static/data/exports/Retro_LD_GE_2014.xlsx
+++ b/static/data/exports/Retro_LD_GE_2014.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_LD_GE_2014.xlsx
+++ b/static/data/exports/Retro_LD_GE_2014.xlsx
@@ -576,6 +576,19 @@
           <t>NCP</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>38</v>
+      </c>
       <c r="Q2" t="b">
         <v>0</v>
       </c>
@@ -638,6 +651,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>31</v>
+      </c>
       <c r="Q3" t="b">
         <v>1</v>
       </c>
@@ -700,6 +726,19 @@
           <t>SP</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>37</v>
+      </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
@@ -762,6 +801,19 @@
           <t>CPI(M)</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>41</v>
+      </c>
       <c r="Q5" t="b">
         <v>0</v>
       </c>
@@ -824,6 +876,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>60</v>
+      </c>
       <c r="Q6" t="b">
         <v>0</v>
       </c>
@@ -885,6 +950,19 @@
         <is>
           <t>CPI</t>
         </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>38</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
